--- a/outputs/q3/carrier_utilization.xlsx
+++ b/outputs/q3/carrier_utilization.xlsx
@@ -503,13 +503,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5988.300000000003</v>
+        <v>5947.13237313028</v>
       </c>
       <c r="D4" t="n">
         <v>6000</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9911887288550467</v>
       </c>
     </row>
     <row r="5">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5994</v>
+        <v>4146.625</v>
       </c>
       <c r="D5" t="n">
         <v>6000</v>
       </c>
       <c r="E5" t="n">
-        <v>0.999</v>
+        <v>0.6911041666666666</v>
       </c>
     </row>
     <row r="6">
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5999.575106100793</v>
+        <v>5999.383275549543</v>
       </c>
       <c r="D7" t="n">
         <v>6000</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9998972125915906</v>
       </c>
     </row>
     <row r="8">
@@ -598,13 +598,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>6000</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -655,13 +655,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5988.300000000003</v>
+        <v>5996.610488352615</v>
       </c>
       <c r="D12" t="n">
         <v>6000</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9994350813921025</v>
       </c>
     </row>
     <row r="13">
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5994</v>
+        <v>3119.058132229553</v>
       </c>
       <c r="D13" t="n">
         <v>6000</v>
       </c>
       <c r="E13" t="n">
-        <v>0.999</v>
+        <v>0.5198430220382588</v>
       </c>
     </row>
     <row r="14">
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5999.575106100793</v>
+        <v>5998.428310978625</v>
       </c>
       <c r="D15" t="n">
         <v>6000</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9997380518297708</v>
       </c>
     </row>
     <row r="16">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>6000</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5988.300000000003</v>
+        <v>5997.884164227719</v>
       </c>
       <c r="D20" t="n">
         <v>6000</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9996473607046199</v>
       </c>
     </row>
     <row r="21">
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5994</v>
+        <v>3889.899485599502</v>
       </c>
       <c r="D21" t="n">
         <v>6000</v>
       </c>
       <c r="E21" t="n">
-        <v>0.999</v>
+        <v>0.6483165809332503</v>
       </c>
     </row>
     <row r="22">
@@ -864,13 +864,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5999.575106100793</v>
+        <v>5997.886696151114</v>
       </c>
       <c r="D23" t="n">
         <v>6000</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9996477826918523</v>
       </c>
     </row>
     <row r="24">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>6000</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5988.300000000003</v>
+        <v>5997.309607711434</v>
       </c>
       <c r="D28" t="n">
         <v>6000</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.999551601285239</v>
       </c>
     </row>
     <row r="29">
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5994</v>
+        <v>3091.082142857143</v>
       </c>
       <c r="D29" t="n">
         <v>6000</v>
       </c>
       <c r="E29" t="n">
-        <v>0.999</v>
+        <v>0.5151803571428573</v>
       </c>
     </row>
     <row r="30">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5999.575106100793</v>
+        <v>5999.904200234194</v>
       </c>
       <c r="D31" t="n">
         <v>6000</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9999840333723656</v>
       </c>
     </row>
     <row r="32">
@@ -1054,13 +1054,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>6000</v>
       </c>
       <c r="E33" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5988.300000000003</v>
+        <v>5989.810444103332</v>
       </c>
       <c r="D36" t="n">
         <v>6000</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9983017406838887</v>
       </c>
     </row>
     <row r="37">
@@ -1130,13 +1130,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5994</v>
+        <v>3995.296593665978</v>
       </c>
       <c r="D37" t="n">
         <v>6000</v>
       </c>
       <c r="E37" t="n">
-        <v>0.999</v>
+        <v>0.6658827656109964</v>
       </c>
     </row>
     <row r="38">
@@ -1168,13 +1168,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5999.575106100793</v>
+        <v>5998.867707531696</v>
       </c>
       <c r="D39" t="n">
         <v>6000</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.999811284588616</v>
       </c>
     </row>
     <row r="40">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>6000</v>
       </c>
       <c r="E41" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5988.300000000003</v>
+        <v>5998.881355461989</v>
       </c>
       <c r="D44" t="n">
         <v>6000</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9998135592436649</v>
       </c>
     </row>
     <row r="45">
@@ -1282,13 +1282,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5994</v>
+        <v>5074.513109552026</v>
       </c>
       <c r="D45" t="n">
         <v>6000</v>
       </c>
       <c r="E45" t="n">
-        <v>0.999</v>
+        <v>0.8457521849253375</v>
       </c>
     </row>
     <row r="46">
@@ -1320,13 +1320,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5999.575106100793</v>
+        <v>5998.628741512022</v>
       </c>
       <c r="D47" t="n">
         <v>6000</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9997714569186704</v>
       </c>
     </row>
     <row r="48">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>6000</v>
       </c>
       <c r="E49" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5988.300000000003</v>
+        <v>5998.095759075861</v>
       </c>
       <c r="D52" t="n">
         <v>6000</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9996826265126435</v>
       </c>
     </row>
     <row r="53">
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5994</v>
+        <v>5018.098770019562</v>
       </c>
       <c r="D53" t="n">
         <v>6000</v>
       </c>
       <c r="E53" t="n">
-        <v>0.999</v>
+        <v>0.8363497950032603</v>
       </c>
     </row>
     <row r="54">
@@ -1472,13 +1472,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5999.575106100793</v>
+        <v>5998.140892552507</v>
       </c>
       <c r="D55" t="n">
         <v>6000</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9996901487587513</v>
       </c>
     </row>
     <row r="56">
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
         <v>6000</v>
       </c>
       <c r="E57" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5988.300000000003</v>
+        <v>5995.680859571967</v>
       </c>
       <c r="D60" t="n">
         <v>6000</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9992801432619944</v>
       </c>
     </row>
     <row r="61">
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5994</v>
+        <v>4994.739382348071</v>
       </c>
       <c r="D61" t="n">
         <v>6000</v>
       </c>
       <c r="E61" t="n">
-        <v>0.999</v>
+        <v>0.8324565637246785</v>
       </c>
     </row>
     <row r="62">
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5999.575106100793</v>
+        <v>5999.635138201105</v>
       </c>
       <c r="D63" t="n">
         <v>6000</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9999391897001842</v>
       </c>
     </row>
     <row r="64">
@@ -1662,13 +1662,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
         <v>6000</v>
       </c>
       <c r="E65" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1719,13 +1719,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5988.300000000003</v>
+        <v>5997.597299774903</v>
       </c>
       <c r="D68" t="n">
         <v>6000</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9995995499624839</v>
       </c>
     </row>
     <row r="69">
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5994</v>
+        <v>5741.935069418182</v>
       </c>
       <c r="D69" t="n">
         <v>6000</v>
       </c>
       <c r="E69" t="n">
-        <v>0.999</v>
+        <v>0.9569891782363636</v>
       </c>
     </row>
     <row r="70">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5999.575106100793</v>
+        <v>5996.78869492269</v>
       </c>
       <c r="D71" t="n">
         <v>6000</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9994647824871151</v>
       </c>
     </row>
     <row r="72">
@@ -1814,13 +1814,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
         <v>6000</v>
       </c>
       <c r="E73" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5988.300000000003</v>
+        <v>5991.589777758913</v>
       </c>
       <c r="D76" t="n">
         <v>6000</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9985982962931521</v>
       </c>
     </row>
     <row r="77">
@@ -1890,13 +1890,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5994</v>
+        <v>5235.151195334528</v>
       </c>
       <c r="D77" t="n">
         <v>6000</v>
       </c>
       <c r="E77" t="n">
-        <v>0.999</v>
+        <v>0.8725251992224213</v>
       </c>
     </row>
     <row r="78">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5999.575106100793</v>
+        <v>5997.625511073222</v>
       </c>
       <c r="D79" t="n">
         <v>6000</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9996042518455369</v>
       </c>
     </row>
     <row r="80">
@@ -1966,13 +1966,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
         <v>6000</v>
       </c>
       <c r="E81" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>5988.300000000003</v>
+        <v>5992.407723675002</v>
       </c>
       <c r="D84" t="n">
         <v>6000</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9987346206125003</v>
       </c>
     </row>
     <row r="85">
@@ -2042,13 +2042,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>5994</v>
+        <v>5872.196967813641</v>
       </c>
       <c r="D85" t="n">
         <v>6000</v>
       </c>
       <c r="E85" t="n">
-        <v>0.999</v>
+        <v>0.9786994946356069</v>
       </c>
     </row>
     <row r="86">
@@ -2080,13 +2080,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5999.575106100793</v>
+        <v>5998.57662747421</v>
       </c>
       <c r="D87" t="n">
         <v>6000</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9997627712457017</v>
       </c>
     </row>
     <row r="88">
@@ -2118,13 +2118,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
         <v>6000</v>
       </c>
       <c r="E89" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5988.300000000003</v>
+        <v>5985.825318646037</v>
       </c>
       <c r="D92" t="n">
         <v>6000</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9976375531076729</v>
       </c>
     </row>
     <row r="93">
@@ -2194,13 +2194,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5994</v>
+        <v>5642.692666397288</v>
       </c>
       <c r="D93" t="n">
         <v>6000</v>
       </c>
       <c r="E93" t="n">
-        <v>0.999</v>
+        <v>0.9404487777328814</v>
       </c>
     </row>
     <row r="94">
@@ -2232,13 +2232,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5999.575106100793</v>
+        <v>5998.62676483963</v>
       </c>
       <c r="D95" t="n">
         <v>6000</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9997711274732716</v>
       </c>
     </row>
     <row r="96">
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
         <v>6000</v>
       </c>
       <c r="E97" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2327,13 +2327,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>5988.300000000003</v>
+        <v>5997.669325724855</v>
       </c>
       <c r="D100" t="n">
         <v>6000</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9996115542874758</v>
       </c>
     </row>
     <row r="101">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>5994</v>
+        <v>5972.568231799861</v>
       </c>
       <c r="D101" t="n">
         <v>6000</v>
       </c>
       <c r="E101" t="n">
-        <v>0.999</v>
+        <v>0.9954280386333101</v>
       </c>
     </row>
     <row r="102">
@@ -2384,13 +2384,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5999.575106100793</v>
+        <v>5999.171008906829</v>
       </c>
       <c r="D103" t="n">
         <v>6000</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9998618348178049</v>
       </c>
     </row>
     <row r="104">
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>279.4</v>
+        <v>395.8900016718977</v>
       </c>
       <c r="D105" t="n">
         <v>6000</v>
       </c>
       <c r="E105" t="n">
-        <v>0.04656666666666667</v>
+        <v>0.06598166694531628</v>
       </c>
     </row>
     <row r="106">
@@ -2479,13 +2479,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>5988.300000000003</v>
+        <v>5999.389907443649</v>
       </c>
       <c r="D108" t="n">
         <v>6000</v>
       </c>
       <c r="E108" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9998983179072749</v>
       </c>
     </row>
     <row r="109">
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5994</v>
+        <v>5998.684383543055</v>
       </c>
       <c r="D109" t="n">
         <v>6000</v>
       </c>
       <c r="E109" t="n">
-        <v>0.999</v>
+        <v>0.9997807305905091</v>
       </c>
     </row>
     <row r="110">
@@ -2536,13 +2536,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>5999.575106100793</v>
+        <v>5997.746435157113</v>
       </c>
       <c r="D111" t="n">
         <v>6000</v>
       </c>
       <c r="E111" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9996244058595187</v>
       </c>
     </row>
     <row r="112">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>279.4</v>
+        <v>707.8661616647323</v>
       </c>
       <c r="D113" t="n">
         <v>6000</v>
       </c>
       <c r="E113" t="n">
-        <v>0.04656666666666667</v>
+        <v>0.1179776936107887</v>
       </c>
     </row>
     <row r="114">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>5988.300000000003</v>
+        <v>5999.612866193822</v>
       </c>
       <c r="D116" t="n">
         <v>6000</v>
       </c>
       <c r="E116" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9999354776989703</v>
       </c>
     </row>
     <row r="117">
@@ -2650,13 +2650,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>5994</v>
+        <v>5974.839722017117</v>
       </c>
       <c r="D117" t="n">
         <v>6000</v>
       </c>
       <c r="E117" t="n">
-        <v>0.999</v>
+        <v>0.9958066203361862</v>
       </c>
     </row>
     <row r="118">
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>5999.575106100793</v>
+        <v>5996.562479751096</v>
       </c>
       <c r="D119" t="n">
         <v>6000</v>
       </c>
       <c r="E119" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9994270799585161</v>
       </c>
     </row>
     <row r="120">
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
         <v>6000</v>
       </c>
       <c r="E121" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>5988.300000000003</v>
+        <v>5998.793124627595</v>
       </c>
       <c r="D124" t="n">
         <v>6000</v>
       </c>
       <c r="E124" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9997988541045991</v>
       </c>
     </row>
     <row r="125">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>5994</v>
+        <v>5249.939328121326</v>
       </c>
       <c r="D125" t="n">
         <v>6000</v>
       </c>
       <c r="E125" t="n">
-        <v>0.999</v>
+        <v>0.874989888020221</v>
       </c>
     </row>
     <row r="126">
@@ -2840,13 +2840,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>5999.575106100793</v>
+        <v>5998.777085273146</v>
       </c>
       <c r="D127" t="n">
         <v>6000</v>
       </c>
       <c r="E127" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9997961808788577</v>
       </c>
     </row>
     <row r="128">
@@ -2878,13 +2878,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D129" t="n">
         <v>6000</v>
       </c>
       <c r="E129" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>5988.300000000003</v>
+        <v>5995.968185444843</v>
       </c>
       <c r="D132" t="n">
         <v>6000</v>
       </c>
       <c r="E132" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9993280309074738</v>
       </c>
     </row>
     <row r="133">
@@ -2954,13 +2954,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>5994</v>
+        <v>5755.124246462589</v>
       </c>
       <c r="D133" t="n">
         <v>6000</v>
       </c>
       <c r="E133" t="n">
-        <v>0.999</v>
+        <v>0.9591873744104316</v>
       </c>
     </row>
     <row r="134">
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>5999.575106100793</v>
+        <v>5997.397335549235</v>
       </c>
       <c r="D135" t="n">
         <v>6000</v>
       </c>
       <c r="E135" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9995662225915393</v>
       </c>
     </row>
     <row r="136">
@@ -3030,13 +3030,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D137" t="n">
         <v>6000</v>
       </c>
       <c r="E137" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>5988.300000000003</v>
+        <v>5996.925593365869</v>
       </c>
       <c r="D140" t="n">
         <v>6000</v>
       </c>
       <c r="E140" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9994875988943115</v>
       </c>
     </row>
     <row r="141">
@@ -3106,13 +3106,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>5994</v>
+        <v>5969.75303091372</v>
       </c>
       <c r="D141" t="n">
         <v>6000</v>
       </c>
       <c r="E141" t="n">
-        <v>0.999</v>
+        <v>0.9949588384856201</v>
       </c>
     </row>
     <row r="142">
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>5999.575106100793</v>
+        <v>5995.823215332768</v>
       </c>
       <c r="D143" t="n">
         <v>6000</v>
       </c>
       <c r="E143" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.999303869222128</v>
       </c>
     </row>
     <row r="144">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>279.4</v>
+        <v>1411.42234784769</v>
       </c>
       <c r="D145" t="n">
         <v>6000</v>
       </c>
       <c r="E145" t="n">
-        <v>0.04656666666666667</v>
+        <v>0.235237057974615</v>
       </c>
     </row>
     <row r="146">
@@ -3239,13 +3239,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>5988.300000000003</v>
+        <v>5995.26498680536</v>
       </c>
       <c r="D148" t="n">
         <v>6000</v>
       </c>
       <c r="E148" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9992108311342266</v>
       </c>
     </row>
     <row r="149">
@@ -3258,13 +3258,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>5994</v>
+        <v>5985.032397049346</v>
       </c>
       <c r="D149" t="n">
         <v>6000</v>
       </c>
       <c r="E149" t="n">
-        <v>0.999</v>
+        <v>0.9975053995082244</v>
       </c>
     </row>
     <row r="150">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>5999.575106100793</v>
+        <v>5994.367930699655</v>
       </c>
       <c r="D151" t="n">
         <v>6000</v>
       </c>
       <c r="E151" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9990613217832758</v>
       </c>
     </row>
     <row r="152">
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>279.4</v>
+        <v>630.3269457576267</v>
       </c>
       <c r="D153" t="n">
         <v>6000</v>
       </c>
       <c r="E153" t="n">
-        <v>0.04656666666666667</v>
+        <v>0.1050544909596045</v>
       </c>
     </row>
     <row r="154">
@@ -3391,13 +3391,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>5988.300000000003</v>
+        <v>5996.506509304045</v>
       </c>
       <c r="D156" t="n">
         <v>6000</v>
       </c>
       <c r="E156" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9994177515506741</v>
       </c>
     </row>
     <row r="157">
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>5994</v>
+        <v>5545.336947607318</v>
       </c>
       <c r="D157" t="n">
         <v>6000</v>
       </c>
       <c r="E157" t="n">
-        <v>0.999</v>
+        <v>0.9242228246012196</v>
       </c>
     </row>
     <row r="158">
@@ -3448,13 +3448,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>5999.575106100793</v>
+        <v>5999.370328847813</v>
       </c>
       <c r="D159" t="n">
         <v>6000</v>
       </c>
       <c r="E159" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9998950548079688</v>
       </c>
     </row>
     <row r="160">
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D161" t="n">
         <v>6000</v>
       </c>
       <c r="E161" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>5988.300000000003</v>
+        <v>5994.60171627045</v>
       </c>
       <c r="D164" t="n">
         <v>6000</v>
       </c>
       <c r="E164" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9991002860450751</v>
       </c>
     </row>
     <row r="165">
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>5994</v>
+        <v>5995.382473517348</v>
       </c>
       <c r="D165" t="n">
         <v>6000</v>
       </c>
       <c r="E165" t="n">
-        <v>0.999</v>
+        <v>0.9992304122528912</v>
       </c>
     </row>
     <row r="166">
@@ -3600,13 +3600,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>5999.575106100793</v>
+        <v>5998.70192894888</v>
       </c>
       <c r="D167" t="n">
         <v>6000</v>
       </c>
       <c r="E167" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9997836548248134</v>
       </c>
     </row>
     <row r="168">
@@ -3638,13 +3638,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>279.4</v>
+        <v>360.8701657458564</v>
       </c>
       <c r="D169" t="n">
         <v>6000</v>
       </c>
       <c r="E169" t="n">
-        <v>0.04656666666666667</v>
+        <v>0.06014502762430939</v>
       </c>
     </row>
     <row r="170">
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>5988.300000000003</v>
+        <v>5994.510662296863</v>
       </c>
       <c r="D172" t="n">
         <v>6000</v>
       </c>
       <c r="E172" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9990851103828106</v>
       </c>
     </row>
     <row r="173">
@@ -3714,13 +3714,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>5994</v>
+        <v>5841.903069075934</v>
       </c>
       <c r="D173" t="n">
         <v>6000</v>
       </c>
       <c r="E173" t="n">
-        <v>0.999</v>
+        <v>0.9736505115126556</v>
       </c>
     </row>
     <row r="174">
@@ -3752,13 +3752,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>5999.575106100793</v>
+        <v>5999.813827153942</v>
       </c>
       <c r="D175" t="n">
         <v>6000</v>
       </c>
       <c r="E175" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9999689711923236</v>
       </c>
     </row>
     <row r="176">
@@ -3790,13 +3790,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D177" t="n">
         <v>6000</v>
       </c>
       <c r="E177" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -3847,13 +3847,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>5988.300000000003</v>
+        <v>5995.288309151943</v>
       </c>
       <c r="D180" t="n">
         <v>6000</v>
       </c>
       <c r="E180" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9992147181919906</v>
       </c>
     </row>
     <row r="181">
@@ -3866,13 +3866,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>5994</v>
+        <v>5810.33826577049</v>
       </c>
       <c r="D181" t="n">
         <v>6000</v>
       </c>
       <c r="E181" t="n">
-        <v>0.999</v>
+        <v>0.9683897109617483</v>
       </c>
     </row>
     <row r="182">
@@ -3904,13 +3904,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>5999.575106100793</v>
+        <v>5998.867149483302</v>
       </c>
       <c r="D183" t="n">
         <v>6000</v>
       </c>
       <c r="E183" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9998111915805502</v>
       </c>
     </row>
     <row r="184">
@@ -3942,13 +3942,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D185" t="n">
         <v>6000</v>
       </c>
       <c r="E185" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -3999,13 +3999,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>5988.300000000003</v>
+        <v>5992.048899266098</v>
       </c>
       <c r="D188" t="n">
         <v>6000</v>
       </c>
       <c r="E188" t="n">
-        <v>0.9980500000000004</v>
+        <v>0.9986748165443496</v>
       </c>
     </row>
     <row r="189">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>5994</v>
+        <v>5723.002281082206</v>
       </c>
       <c r="D189" t="n">
         <v>6000</v>
       </c>
       <c r="E189" t="n">
-        <v>0.999</v>
+        <v>0.9538337135137009</v>
       </c>
     </row>
     <row r="190">
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>5999.575106100793</v>
+        <v>5997.15874609726</v>
       </c>
       <c r="D191" t="n">
         <v>6000</v>
       </c>
       <c r="E191" t="n">
-        <v>0.9999291843501322</v>
+        <v>0.9995264576828766</v>
       </c>
     </row>
     <row r="192">
@@ -4094,13 +4094,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>279.4</v>
+        <v>0</v>
       </c>
       <c r="D193" t="n">
         <v>6000</v>
       </c>
       <c r="E193" t="n">
-        <v>0.04656666666666667</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
